--- a/templates/cimb-bulk-email.xlsx
+++ b/templates/cimb-bulk-email.xlsx
@@ -9,24 +9,41 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <fonts count="3">
+  <numFmts count="2">
+    <numFmt numFmtId="176" formatCode="#,##0.00;[Red]#,##0.00"/>
+    <numFmt numFmtId="177" formatCode="dd\/mm\/yyyy"/>
+  </numFmts>
+  <fonts count="5">
     <font>
       <sz val="11"/>
       <name val="Calibri"/>
     </font>
     <font>
-      <sz val="9"/>
-      <color rgb="FF555555"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <b/>
+      <sz val="10"/>
+      <color rgb="FF000000"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
       <sz val="11"/>
-      <color rgb="FFC00000"/>
-      <name val="Calibri"/>
+      <color rgb="FFFF0000"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FF0000FF"/>
+      <name val="Arial"/>
+      <family val="2"/>
     </font>
   </fonts>
-  <fills count="4">
+  <fills count="3">
     <fill>
       <patternFill/>
     </fill>
@@ -35,13 +52,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFCE4D6"/>
+        <fgColor rgb="FF969696"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -73,13 +84,48 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+  <cellXfs count="14">
+    <xf numFmtId="1" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="bottom"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyNumberFormat="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyNumberFormat="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyNumberFormat="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyNumberFormat="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyNumberFormat="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="bottom"/>
+    </xf>
+    <xf numFmtId="49" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="bottom"/>
+    </xf>
+    <xf numFmtId="176" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="bottom"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="bottom"/>
+    </xf>
+    <xf numFmtId="177" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyNumberFormat="1" applyAlignment="1">
+      <alignment vertical="bottom"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -90,84 +136,84 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:M3"/>
+  <dimension ref="A1:M4"/>
   <sheetFormatPr defaultRowHeight="15"/>
-  <col min="1" max="1" width="37.3" customWidth="1"/>
-  <col min="2" max="2" width="30.7" customWidth="1"/>
-  <col min="3" max="3" width="19.6" customWidth="1"/>
+  <col min="1" max="1" width="37.29" customWidth="1"/>
+  <col min="2" max="2" width="30.71" customWidth="1"/>
+  <col min="3" max="3" width="19.57" customWidth="1"/>
   <col min="4" max="4" width="22" customWidth="1"/>
   <col min="5" max="5" width="21" customWidth="1"/>
-  <col min="6" max="6" width="31.3" customWidth="1"/>
-  <col min="7" max="7" width="28.3" customWidth="1"/>
-  <col min="8" max="8" width="15.7" customWidth="1"/>
-  <col min="9" max="9" width="16.7" customWidth="1"/>
-  <col min="10" max="10" width="16.7" customWidth="1"/>
-  <col min="11" max="11" width="24.4" customWidth="1"/>
-  <col min="12" max="12" width="39.7" customWidth="1"/>
+  <col min="6" max="6" width="31.29" customWidth="1"/>
+  <col min="7" max="7" width="28.29" customWidth="1"/>
+  <col min="8" max="8" width="15.71" customWidth="1"/>
+  <col min="9" max="9" width="16.71" customWidth="1"/>
+  <col min="10" max="10" width="16.71" customWidth="1"/>
+  <col min="11" max="11" width="24.43" customWidth="1"/>
+  <col min="12" max="12" width="39.71" customWidth="1"/>
   <col min="13" max="13" width="22" customWidth="1"/>
   <sheetData>
-    <row r="1" ht="15" customHeight="1">
-      <c r="A1" s="1" t="inlineStr">
+    <row r="1" ht="15" customHeight="1" hidden="1">
+      <c r="A1" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">40</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">20</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">2</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">16</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">11</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">30</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">70</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H1" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">5</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="I1" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">20</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="J1" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">30</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="K1" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">8</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="L1" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">500</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="M1" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">11</t>
         </is>
@@ -189,7 +235,7 @@
           <t xml:space="preserve">Length: 2 (Num Only)</t>
         </is>
       </c>
-      <c r="D2" s="1" t="inlineStr">
+      <c r="D2" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">Length: 16 (Num only)</t>
         </is>
@@ -241,17 +287,17 @@
       </c>
     </row>
     <row r="3" ht="42.75" customHeight="1">
-      <c r="A3" s="2" t="inlineStr">
+      <c r="A3" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">*Beneficiary Name</t>
         </is>
       </c>
-      <c r="B3" s="2" t="inlineStr">
+      <c r="B3" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">Beneficiary ID</t>
         </is>
       </c>
-      <c r="C3" s="2" t="inlineStr">
+      <c r="C3" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">*BNM Code</t>
         </is>
@@ -261,53 +307,68 @@
           <t xml:space="preserve">*Account Number</t>
         </is>
       </c>
-      <c r="E3" s="2" t="inlineStr">
+      <c r="E3" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">*Payment Amount</t>
         </is>
       </c>
-      <c r="F3" s="2" t="inlineStr">
+      <c r="F3" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">Reference Number</t>
         </is>
       </c>
-      <c r="G3" s="2" t="inlineStr">
+      <c r="G3" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">*Beneficiary Email Address</t>
         </is>
       </c>
-      <c r="H3" s="2" t="inlineStr">
+      <c r="H3" s="5" t="inlineStr">
         <is>
           <t xml:space="preserve">*Payment Reference 
 Number</t>
         </is>
       </c>
-      <c r="I3" s="2" t="inlineStr">
+      <c r="I3" s="6" t="inlineStr">
         <is>
           <t xml:space="preserve">Payment Description</t>
         </is>
       </c>
-      <c r="J3" s="2" t="inlineStr">
+      <c r="J3" s="5" t="inlineStr">
         <is>
           <t xml:space="preserve">*Payment Detail Number</t>
         </is>
       </c>
-      <c r="K3" s="2" t="inlineStr">
+      <c r="K3" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">*Payment Detail Date 
 (DD/MM/YYYY)</t>
         </is>
       </c>
-      <c r="L3" s="2" t="inlineStr">
+      <c r="L3" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">*Payment Description</t>
         </is>
       </c>
-      <c r="M3" s="2" t="inlineStr">
+      <c r="M3" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">*Payment Detail Amount</t>
         </is>
       </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="9"/>
+      <c r="B4" s="10"/>
+      <c r="C4" s="9"/>
+      <c r="D4" s="10"/>
+      <c r="E4" s="11"/>
+      <c r="F4" s="10"/>
+      <c r="G4" s="12"/>
+      <c r="H4" s="10"/>
+      <c r="I4" s="9"/>
+      <c r="J4" s="10"/>
+      <c r="K4" s="13"/>
+      <c r="L4" s="9"/>
+      <c r="M4" s="11"/>
     </row>
   </sheetData>
 </worksheet>
